--- a/src/outputs/ss-mid-sem-ta_schedule-final.xlsx
+++ b/src/outputs/ss-mid-sem-ta_schedule-final.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEC8874-C82F-42C9-B3EA-B5F242164FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="TA Schedule" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Sessions Count" state="visible" r:id="rId5"/>
+    <sheet name="TA Schedule" sheetId="1" r:id="rId1"/>
+    <sheet name="Sessions Count" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2994" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2994" uniqueCount="233">
   <si>
     <t>Date</t>
   </si>
@@ -708,19 +712,22 @@
   </si>
   <si>
     <t>Total Sessions</t>
+  </si>
+  <si>
+    <t>Nimatu Hussein</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1083,16 +1090,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D749"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="1" max="1" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1106,7 +1114,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1120,7 +1128,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1134,7 +1142,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1148,7 +1156,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1162,7 +1170,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1176,7 +1184,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1190,7 +1198,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1204,7 +1212,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1218,7 +1226,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1232,7 +1240,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1246,7 +1254,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1260,7 +1268,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1274,7 +1282,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1288,7 +1296,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1302,7 +1310,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1316,7 +1324,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1330,7 +1338,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1344,7 +1352,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1358,7 +1366,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1372,7 +1380,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1386,7 +1394,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1400,7 +1408,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1414,7 +1422,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1428,7 +1436,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1442,7 +1450,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1456,7 +1464,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1470,7 +1478,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1484,7 +1492,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1498,7 +1506,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -1512,7 +1520,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -1526,7 +1534,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -1540,7 +1548,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -1554,7 +1562,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -1568,7 +1576,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -1582,7 +1590,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -1596,7 +1604,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -1610,7 +1618,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -1624,7 +1632,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -1638,7 +1646,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -1652,7 +1660,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -1666,7 +1674,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -1680,7 +1688,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -1694,7 +1702,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -1708,7 +1716,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -1722,7 +1730,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -1736,7 +1744,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>4</v>
       </c>
@@ -1750,7 +1758,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -1764,7 +1772,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -1778,7 +1786,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -1792,7 +1800,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -1806,7 +1814,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -1820,7 +1828,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>4</v>
       </c>
@@ -1834,7 +1842,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -1848,7 +1856,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>4</v>
       </c>
@@ -1862,7 +1870,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -1876,7 +1884,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>4</v>
       </c>
@@ -1890,7 +1898,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -1904,7 +1912,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -1918,7 +1926,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>4</v>
       </c>
@@ -1932,7 +1940,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>4</v>
       </c>
@@ -1946,7 +1954,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>4</v>
       </c>
@@ -1960,7 +1968,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>4</v>
       </c>
@@ -1974,7 +1982,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>4</v>
       </c>
@@ -1988,7 +1996,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>4</v>
       </c>
@@ -2002,7 +2010,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>4</v>
       </c>
@@ -2016,7 +2024,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>4</v>
       </c>
@@ -2030,7 +2038,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>4</v>
       </c>
@@ -2044,7 +2052,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>4</v>
       </c>
@@ -2058,7 +2066,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>4</v>
       </c>
@@ -2072,7 +2080,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>4</v>
       </c>
@@ -2086,7 +2094,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>4</v>
       </c>
@@ -2100,7 +2108,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>4</v>
       </c>
@@ -2114,7 +2122,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>4</v>
       </c>
@@ -2128,7 +2136,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>4</v>
       </c>
@@ -2142,7 +2150,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>4</v>
       </c>
@@ -2156,7 +2164,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>4</v>
       </c>
@@ -2170,7 +2178,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>4</v>
       </c>
@@ -2184,7 +2192,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -2198,7 +2206,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>4</v>
       </c>
@@ -2212,7 +2220,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>4</v>
       </c>
@@ -2226,7 +2234,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>4</v>
       </c>
@@ -2240,7 +2248,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>4</v>
       </c>
@@ -2254,7 +2262,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>4</v>
       </c>
@@ -2268,7 +2276,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>4</v>
       </c>
@@ -2282,7 +2290,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>4</v>
       </c>
@@ -2296,7 +2304,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>4</v>
       </c>
@@ -2310,7 +2318,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -2324,7 +2332,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>4</v>
       </c>
@@ -2338,7 +2346,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>4</v>
       </c>
@@ -2352,7 +2360,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>4</v>
       </c>
@@ -2366,7 +2374,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>4</v>
       </c>
@@ -2380,7 +2388,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>4</v>
       </c>
@@ -2394,7 +2402,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>4</v>
       </c>
@@ -2408,7 +2416,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>4</v>
       </c>
@@ -2422,7 +2430,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>4</v>
       </c>
@@ -2436,7 +2444,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>4</v>
       </c>
@@ -2450,7 +2458,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>4</v>
       </c>
@@ -2464,7 +2472,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>4</v>
       </c>
@@ -2478,7 +2486,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>4</v>
       </c>
@@ -2492,7 +2500,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>4</v>
       </c>
@@ -2506,7 +2514,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>4</v>
       </c>
@@ -2520,7 +2528,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>4</v>
       </c>
@@ -2534,7 +2542,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>4</v>
       </c>
@@ -2548,7 +2556,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>4</v>
       </c>
@@ -2562,7 +2570,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>4</v>
       </c>
@@ -2576,7 +2584,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>4</v>
       </c>
@@ -2590,7 +2598,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>4</v>
       </c>
@@ -2604,7 +2612,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>4</v>
       </c>
@@ -2618,7 +2626,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>4</v>
       </c>
@@ -2632,7 +2640,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>4</v>
       </c>
@@ -2646,7 +2654,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>4</v>
       </c>
@@ -2660,7 +2668,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>4</v>
       </c>
@@ -2674,7 +2682,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>4</v>
       </c>
@@ -2688,7 +2696,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>4</v>
       </c>
@@ -2702,7 +2710,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>4</v>
       </c>
@@ -2716,7 +2724,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>4</v>
       </c>
@@ -2730,7 +2738,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>4</v>
       </c>
@@ -2744,7 +2752,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>4</v>
       </c>
@@ -2758,7 +2766,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>4</v>
       </c>
@@ -2772,7 +2780,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>4</v>
       </c>
@@ -2786,7 +2794,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>4</v>
       </c>
@@ -2800,7 +2808,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>4</v>
       </c>
@@ -2814,7 +2822,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>4</v>
       </c>
@@ -2828,7 +2836,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>4</v>
       </c>
@@ -2842,7 +2850,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>4</v>
       </c>
@@ -2856,7 +2864,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>4</v>
       </c>
@@ -2870,7 +2878,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>4</v>
       </c>
@@ -2884,7 +2892,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>4</v>
       </c>
@@ -2898,7 +2906,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>4</v>
       </c>
@@ -2912,7 +2920,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>4</v>
       </c>
@@ -2926,7 +2934,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>4</v>
       </c>
@@ -2940,7 +2948,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>4</v>
       </c>
@@ -2954,7 +2962,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>4</v>
       </c>
@@ -2968,7 +2976,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>4</v>
       </c>
@@ -2982,7 +2990,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>4</v>
       </c>
@@ -2996,7 +3004,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>4</v>
       </c>
@@ -3010,7 +3018,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>4</v>
       </c>
@@ -3024,7 +3032,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>4</v>
       </c>
@@ -3038,7 +3046,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>4</v>
       </c>
@@ -3052,7 +3060,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>4</v>
       </c>
@@ -3066,7 +3074,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>4</v>
       </c>
@@ -3080,7 +3088,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>4</v>
       </c>
@@ -3094,7 +3102,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>4</v>
       </c>
@@ -3108,7 +3116,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>4</v>
       </c>
@@ -3122,7 +3130,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -3136,7 +3144,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>149</v>
       </c>
@@ -3150,7 +3158,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>149</v>
       </c>
@@ -3164,7 +3172,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>149</v>
       </c>
@@ -3178,7 +3186,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>149</v>
       </c>
@@ -3192,7 +3200,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>149</v>
       </c>
@@ -3206,7 +3214,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>149</v>
       </c>
@@ -3220,7 +3228,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>149</v>
       </c>
@@ -3234,7 +3242,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>149</v>
       </c>
@@ -3248,7 +3256,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>149</v>
       </c>
@@ -3262,7 +3270,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>149</v>
       </c>
@@ -3276,7 +3284,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>149</v>
       </c>
@@ -3290,7 +3298,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>149</v>
       </c>
@@ -3304,7 +3312,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>149</v>
       </c>
@@ -3318,7 +3326,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>149</v>
       </c>
@@ -3332,7 +3340,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>149</v>
       </c>
@@ -3346,7 +3354,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>149</v>
       </c>
@@ -3360,7 +3368,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>149</v>
       </c>
@@ -3374,7 +3382,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>149</v>
       </c>
@@ -3388,7 +3396,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>149</v>
       </c>
@@ -3402,7 +3410,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>149</v>
       </c>
@@ -3416,7 +3424,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>149</v>
       </c>
@@ -3430,7 +3438,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>149</v>
       </c>
@@ -3444,7 +3452,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>149</v>
       </c>
@@ -3458,7 +3466,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>149</v>
       </c>
@@ -3472,7 +3480,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>149</v>
       </c>
@@ -3486,7 +3494,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>149</v>
       </c>
@@ -3500,7 +3508,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>149</v>
       </c>
@@ -3514,7 +3522,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>149</v>
       </c>
@@ -3528,7 +3536,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>149</v>
       </c>
@@ -3542,7 +3550,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>149</v>
       </c>
@@ -3556,7 +3564,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>149</v>
       </c>
@@ -3570,7 +3578,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>149</v>
       </c>
@@ -3584,7 +3592,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>149</v>
       </c>
@@ -3598,7 +3606,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>149</v>
       </c>
@@ -3612,7 +3620,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>149</v>
       </c>
@@ -3626,7 +3634,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>149</v>
       </c>
@@ -3640,7 +3648,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>149</v>
       </c>
@@ -3654,7 +3662,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>149</v>
       </c>
@@ -3668,7 +3676,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>149</v>
       </c>
@@ -3682,7 +3690,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>149</v>
       </c>
@@ -3696,7 +3704,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>149</v>
       </c>
@@ -3710,7 +3718,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>149</v>
       </c>
@@ -3724,7 +3732,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>149</v>
       </c>
@@ -3738,7 +3746,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>149</v>
       </c>
@@ -3752,7 +3760,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>149</v>
       </c>
@@ -3766,7 +3774,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>149</v>
       </c>
@@ -3780,7 +3788,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>149</v>
       </c>
@@ -3794,7 +3802,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>149</v>
       </c>
@@ -3808,7 +3816,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>149</v>
       </c>
@@ -3822,7 +3830,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>149</v>
       </c>
@@ -3836,7 +3844,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>149</v>
       </c>
@@ -3850,7 +3858,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>149</v>
       </c>
@@ -3864,7 +3872,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>149</v>
       </c>
@@ -3878,7 +3886,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>149</v>
       </c>
@@ -3892,7 +3900,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>149</v>
       </c>
@@ -3906,7 +3914,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>149</v>
       </c>
@@ -3920,7 +3928,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>149</v>
       </c>
@@ -3934,7 +3942,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>149</v>
       </c>
@@ -3948,7 +3956,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>149</v>
       </c>
@@ -3962,7 +3970,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>149</v>
       </c>
@@ -3976,7 +3984,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>149</v>
       </c>
@@ -3990,7 +3998,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>149</v>
       </c>
@@ -4004,7 +4012,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>149</v>
       </c>
@@ -4018,7 +4026,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>149</v>
       </c>
@@ -4032,7 +4040,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>149</v>
       </c>
@@ -4046,7 +4054,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>149</v>
       </c>
@@ -4060,7 +4068,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>149</v>
       </c>
@@ -4074,7 +4082,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>149</v>
       </c>
@@ -4088,7 +4096,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>149</v>
       </c>
@@ -4102,7 +4110,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>149</v>
       </c>
@@ -4116,7 +4124,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>149</v>
       </c>
@@ -4130,7 +4138,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>149</v>
       </c>
@@ -4144,7 +4152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>149</v>
       </c>
@@ -4158,7 +4166,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>149</v>
       </c>
@@ -4172,7 +4180,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>149</v>
       </c>
@@ -4186,7 +4194,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>149</v>
       </c>
@@ -4200,7 +4208,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>149</v>
       </c>
@@ -4214,7 +4222,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>149</v>
       </c>
@@ -4228,7 +4236,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>149</v>
       </c>
@@ -4242,7 +4250,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>149</v>
       </c>
@@ -4256,7 +4264,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>149</v>
       </c>
@@ -4270,7 +4278,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>149</v>
       </c>
@@ -4284,7 +4292,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>149</v>
       </c>
@@ -4298,7 +4306,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>149</v>
       </c>
@@ -4312,7 +4320,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>149</v>
       </c>
@@ -4326,7 +4334,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>149</v>
       </c>
@@ -4340,7 +4348,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>149</v>
       </c>
@@ -4354,7 +4362,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>149</v>
       </c>
@@ -4368,7 +4376,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>149</v>
       </c>
@@ -4382,7 +4390,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>149</v>
       </c>
@@ -4396,7 +4404,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>149</v>
       </c>
@@ -4410,7 +4418,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>149</v>
       </c>
@@ -4424,7 +4432,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>149</v>
       </c>
@@ -4438,7 +4446,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>149</v>
       </c>
@@ -4452,7 +4460,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>149</v>
       </c>
@@ -4466,7 +4474,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>149</v>
       </c>
@@ -4480,7 +4488,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>149</v>
       </c>
@@ -4494,7 +4502,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>149</v>
       </c>
@@ -4508,7 +4516,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>149</v>
       </c>
@@ -4522,7 +4530,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>149</v>
       </c>
@@ -4536,7 +4544,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>149</v>
       </c>
@@ -4550,7 +4558,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>149</v>
       </c>
@@ -4564,7 +4572,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>149</v>
       </c>
@@ -4578,7 +4586,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>149</v>
       </c>
@@ -4592,7 +4600,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>149</v>
       </c>
@@ -4606,7 +4614,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>149</v>
       </c>
@@ -4620,7 +4628,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>149</v>
       </c>
@@ -4634,7 +4642,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>149</v>
       </c>
@@ -4648,7 +4656,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>149</v>
       </c>
@@ -4662,7 +4670,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>149</v>
       </c>
@@ -4676,7 +4684,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>149</v>
       </c>
@@ -4690,7 +4698,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>149</v>
       </c>
@@ -4704,7 +4712,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>149</v>
       </c>
@@ -4718,7 +4726,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>149</v>
       </c>
@@ -4732,7 +4740,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>149</v>
       </c>
@@ -4746,7 +4754,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>149</v>
       </c>
@@ -4760,7 +4768,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>149</v>
       </c>
@@ -4774,7 +4782,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>149</v>
       </c>
@@ -4788,7 +4796,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>149</v>
       </c>
@@ -4802,7 +4810,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>149</v>
       </c>
@@ -4816,7 +4824,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>149</v>
       </c>
@@ -4830,7 +4838,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>149</v>
       </c>
@@ -4844,7 +4852,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>149</v>
       </c>
@@ -4858,7 +4866,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>149</v>
       </c>
@@ -4872,7 +4880,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>149</v>
       </c>
@@ -4886,7 +4894,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>149</v>
       </c>
@@ -4900,7 +4908,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>149</v>
       </c>
@@ -4914,7 +4922,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>149</v>
       </c>
@@ -4928,7 +4936,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>149</v>
       </c>
@@ -4942,7 +4950,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>149</v>
       </c>
@@ -4956,7 +4964,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>149</v>
       </c>
@@ -4970,7 +4978,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>149</v>
       </c>
@@ -4984,7 +4992,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>149</v>
       </c>
@@ -4998,7 +5006,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>149</v>
       </c>
@@ -5012,7 +5020,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>149</v>
       </c>
@@ -5026,7 +5034,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>149</v>
       </c>
@@ -5040,7 +5048,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>149</v>
       </c>
@@ -5054,7 +5062,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>149</v>
       </c>
@@ -5068,7 +5076,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>149</v>
       </c>
@@ -5082,7 +5090,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>149</v>
       </c>
@@ -5096,7 +5104,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>149</v>
       </c>
@@ -5110,7 +5118,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>149</v>
       </c>
@@ -5124,7 +5132,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>149</v>
       </c>
@@ -5138,7 +5146,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>149</v>
       </c>
@@ -5152,7 +5160,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>149</v>
       </c>
@@ -5166,7 +5174,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>149</v>
       </c>
@@ -5180,7 +5188,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>187</v>
       </c>
@@ -5194,7 +5202,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>187</v>
       </c>
@@ -5208,7 +5216,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>187</v>
       </c>
@@ -5222,7 +5230,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>187</v>
       </c>
@@ -5236,7 +5244,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>187</v>
       </c>
@@ -5250,7 +5258,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>187</v>
       </c>
@@ -5264,7 +5272,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>187</v>
       </c>
@@ -5278,7 +5286,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>187</v>
       </c>
@@ -5292,7 +5300,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>187</v>
       </c>
@@ -5306,7 +5314,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>187</v>
       </c>
@@ -5320,7 +5328,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>187</v>
       </c>
@@ -5334,7 +5342,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>187</v>
       </c>
@@ -5348,7 +5356,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>187</v>
       </c>
@@ -5362,7 +5370,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>187</v>
       </c>
@@ -5376,7 +5384,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>187</v>
       </c>
@@ -5390,7 +5398,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>187</v>
       </c>
@@ -5404,7 +5412,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>187</v>
       </c>
@@ -5418,7 +5426,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>187</v>
       </c>
@@ -5432,7 +5440,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>187</v>
       </c>
@@ -5446,7 +5454,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>187</v>
       </c>
@@ -5460,7 +5468,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>187</v>
       </c>
@@ -5474,7 +5482,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>187</v>
       </c>
@@ -5488,7 +5496,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>187</v>
       </c>
@@ -5502,7 +5510,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>187</v>
       </c>
@@ -5516,7 +5524,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>187</v>
       </c>
@@ -5530,7 +5538,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>187</v>
       </c>
@@ -5544,7 +5552,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>187</v>
       </c>
@@ -5558,7 +5566,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>187</v>
       </c>
@@ -5572,7 +5580,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>187</v>
       </c>
@@ -5586,7 +5594,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>187</v>
       </c>
@@ -5600,7 +5608,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>187</v>
       </c>
@@ -5614,7 +5622,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>187</v>
       </c>
@@ -5628,7 +5636,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>187</v>
       </c>
@@ -5642,7 +5650,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>187</v>
       </c>
@@ -5656,7 +5664,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>187</v>
       </c>
@@ -5670,7 +5678,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>187</v>
       </c>
@@ -5684,7 +5692,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>187</v>
       </c>
@@ -5698,7 +5706,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>187</v>
       </c>
@@ -5712,7 +5720,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>187</v>
       </c>
@@ -5726,7 +5734,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>187</v>
       </c>
@@ -5740,7 +5748,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>187</v>
       </c>
@@ -5754,7 +5762,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>187</v>
       </c>
@@ -5768,7 +5776,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>187</v>
       </c>
@@ -5782,7 +5790,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>187</v>
       </c>
@@ -5796,7 +5804,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>187</v>
       </c>
@@ -5810,7 +5818,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>187</v>
       </c>
@@ -5824,7 +5832,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>187</v>
       </c>
@@ -5838,7 +5846,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>187</v>
       </c>
@@ -5852,7 +5860,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>187</v>
       </c>
@@ -5866,7 +5874,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>187</v>
       </c>
@@ -5880,7 +5888,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>187</v>
       </c>
@@ -5894,7 +5902,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>187</v>
       </c>
@@ -5908,7 +5916,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>187</v>
       </c>
@@ -5922,7 +5930,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>187</v>
       </c>
@@ -5936,7 +5944,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>187</v>
       </c>
@@ -5950,7 +5958,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>187</v>
       </c>
@@ -5964,7 +5972,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>187</v>
       </c>
@@ -5978,7 +5986,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>187</v>
       </c>
@@ -5992,7 +6000,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>187</v>
       </c>
@@ -6006,7 +6014,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>187</v>
       </c>
@@ -6020,7 +6028,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>187</v>
       </c>
@@ -6034,7 +6042,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>187</v>
       </c>
@@ -6048,7 +6056,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>187</v>
       </c>
@@ -6062,7 +6070,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>187</v>
       </c>
@@ -6076,7 +6084,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>187</v>
       </c>
@@ -6090,7 +6098,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>187</v>
       </c>
@@ -6104,7 +6112,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>187</v>
       </c>
@@ -6118,7 +6126,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>187</v>
       </c>
@@ -6132,7 +6140,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>187</v>
       </c>
@@ -6146,7 +6154,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>187</v>
       </c>
@@ -6160,7 +6168,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>187</v>
       </c>
@@ -6174,7 +6182,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>187</v>
       </c>
@@ -6188,7 +6196,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>187</v>
       </c>
@@ -6202,7 +6210,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>187</v>
       </c>
@@ -6216,7 +6224,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>187</v>
       </c>
@@ -6230,7 +6238,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>187</v>
       </c>
@@ -6244,7 +6252,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>187</v>
       </c>
@@ -6258,7 +6266,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>187</v>
       </c>
@@ -6272,7 +6280,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>187</v>
       </c>
@@ -6286,7 +6294,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>187</v>
       </c>
@@ -6300,7 +6308,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>187</v>
       </c>
@@ -6314,7 +6322,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>187</v>
       </c>
@@ -6328,7 +6336,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>187</v>
       </c>
@@ -6342,7 +6350,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>187</v>
       </c>
@@ -6356,7 +6364,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>187</v>
       </c>
@@ -6370,7 +6378,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>187</v>
       </c>
@@ -6384,7 +6392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>187</v>
       </c>
@@ -6398,7 +6406,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>187</v>
       </c>
@@ -6412,7 +6420,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>187</v>
       </c>
@@ -6426,7 +6434,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>187</v>
       </c>
@@ -6440,7 +6448,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>187</v>
       </c>
@@ -6454,7 +6462,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>187</v>
       </c>
@@ -6468,7 +6476,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>187</v>
       </c>
@@ -6482,7 +6490,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>187</v>
       </c>
@@ -6496,7 +6504,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>187</v>
       </c>
@@ -6510,7 +6518,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>187</v>
       </c>
@@ -6524,7 +6532,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>187</v>
       </c>
@@ -6538,7 +6546,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>187</v>
       </c>
@@ -6552,7 +6560,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>187</v>
       </c>
@@ -6566,7 +6574,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>187</v>
       </c>
@@ -6580,7 +6588,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>187</v>
       </c>
@@ -6594,7 +6602,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>187</v>
       </c>
@@ -6608,7 +6616,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>187</v>
       </c>
@@ -6622,7 +6630,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>187</v>
       </c>
@@ -6636,7 +6644,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>187</v>
       </c>
@@ -6650,7 +6658,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>187</v>
       </c>
@@ -6664,7 +6672,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>187</v>
       </c>
@@ -6678,7 +6686,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>187</v>
       </c>
@@ -6692,7 +6700,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>187</v>
       </c>
@@ -6706,7 +6714,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>187</v>
       </c>
@@ -6720,7 +6728,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>187</v>
       </c>
@@ -6734,7 +6742,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>187</v>
       </c>
@@ -6748,7 +6756,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>187</v>
       </c>
@@ -6762,7 +6770,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>187</v>
       </c>
@@ -6776,7 +6784,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>187</v>
       </c>
@@ -6790,7 +6798,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>187</v>
       </c>
@@ -6804,7 +6812,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>187</v>
       </c>
@@ -6818,7 +6826,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>187</v>
       </c>
@@ -6832,7 +6840,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>187</v>
       </c>
@@ -6846,7 +6854,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>187</v>
       </c>
@@ -6860,7 +6868,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>187</v>
       </c>
@@ -6874,7 +6882,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>187</v>
       </c>
@@ -6888,7 +6896,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>187</v>
       </c>
@@ -6902,7 +6910,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>187</v>
       </c>
@@ -6916,7 +6924,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>187</v>
       </c>
@@ -6930,7 +6938,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>187</v>
       </c>
@@ -6944,7 +6952,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>187</v>
       </c>
@@ -6958,7 +6966,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>187</v>
       </c>
@@ -6972,7 +6980,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>187</v>
       </c>
@@ -6986,7 +6994,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>187</v>
       </c>
@@ -7000,7 +7008,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>187</v>
       </c>
@@ -7014,7 +7022,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>187</v>
       </c>
@@ -7028,7 +7036,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>187</v>
       </c>
@@ -7042,7 +7050,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>187</v>
       </c>
@@ -7056,7 +7064,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>187</v>
       </c>
@@ -7070,7 +7078,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>187</v>
       </c>
@@ -7084,7 +7092,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>187</v>
       </c>
@@ -7098,7 +7106,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>187</v>
       </c>
@@ -7112,7 +7120,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>187</v>
       </c>
@@ -7126,7 +7134,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>187</v>
       </c>
@@ -7140,7 +7148,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>187</v>
       </c>
@@ -7154,7 +7162,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>187</v>
       </c>
@@ -7168,7 +7176,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>187</v>
       </c>
@@ -7182,7 +7190,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>187</v>
       </c>
@@ -7196,7 +7204,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>187</v>
       </c>
@@ -7210,7 +7218,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>187</v>
       </c>
@@ -7224,7 +7232,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>204</v>
       </c>
@@ -7238,7 +7246,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>204</v>
       </c>
@@ -7252,7 +7260,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>204</v>
       </c>
@@ -7266,7 +7274,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>204</v>
       </c>
@@ -7280,7 +7288,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>204</v>
       </c>
@@ -7294,7 +7302,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>204</v>
       </c>
@@ -7308,7 +7316,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>204</v>
       </c>
@@ -7322,7 +7330,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>204</v>
       </c>
@@ -7336,7 +7344,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>204</v>
       </c>
@@ -7350,7 +7358,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>204</v>
       </c>
@@ -7364,7 +7372,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>204</v>
       </c>
@@ -7378,7 +7386,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>204</v>
       </c>
@@ -7392,7 +7400,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>204</v>
       </c>
@@ -7406,7 +7414,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>204</v>
       </c>
@@ -7420,7 +7428,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>204</v>
       </c>
@@ -7434,7 +7442,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>204</v>
       </c>
@@ -7448,7 +7456,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>204</v>
       </c>
@@ -7462,7 +7470,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>204</v>
       </c>
@@ -7476,7 +7484,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>204</v>
       </c>
@@ -7490,7 +7498,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>204</v>
       </c>
@@ -7504,7 +7512,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>204</v>
       </c>
@@ -7518,7 +7526,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>204</v>
       </c>
@@ -7532,7 +7540,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>204</v>
       </c>
@@ -7546,7 +7554,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>204</v>
       </c>
@@ -7560,7 +7568,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
         <v>204</v>
       </c>
@@ -7574,7 +7582,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
         <v>204</v>
       </c>
@@ -7588,7 +7596,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>204</v>
       </c>
@@ -7602,7 +7610,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
         <v>204</v>
       </c>
@@ -7616,7 +7624,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>204</v>
       </c>
@@ -7630,7 +7638,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>204</v>
       </c>
@@ -7644,7 +7652,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>204</v>
       </c>
@@ -7658,7 +7666,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>204</v>
       </c>
@@ -7672,7 +7680,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>204</v>
       </c>
@@ -7686,7 +7694,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>204</v>
       </c>
@@ -7700,7 +7708,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>204</v>
       </c>
@@ -7714,7 +7722,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>204</v>
       </c>
@@ -7728,7 +7736,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>204</v>
       </c>
@@ -7742,7 +7750,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>204</v>
       </c>
@@ -7756,7 +7764,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>204</v>
       </c>
@@ -7770,7 +7778,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>204</v>
       </c>
@@ -7784,7 +7792,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>204</v>
       </c>
@@ -7798,7 +7806,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>204</v>
       </c>
@@ -7812,7 +7820,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>204</v>
       </c>
@@ -7826,7 +7834,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>204</v>
       </c>
@@ -7840,7 +7848,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>204</v>
       </c>
@@ -7854,7 +7862,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>204</v>
       </c>
@@ -7868,7 +7876,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>204</v>
       </c>
@@ -7882,7 +7890,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>204</v>
       </c>
@@ -7896,7 +7904,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
         <v>204</v>
       </c>
@@ -7910,7 +7918,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
         <v>204</v>
       </c>
@@ -7924,7 +7932,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
         <v>204</v>
       </c>
@@ -7938,7 +7946,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
         <v>204</v>
       </c>
@@ -7952,7 +7960,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>204</v>
       </c>
@@ -7966,7 +7974,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>204</v>
       </c>
@@ -7980,7 +7988,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>204</v>
       </c>
@@ -7994,7 +8002,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>204</v>
       </c>
@@ -8008,7 +8016,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
         <v>204</v>
       </c>
@@ -8022,7 +8030,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
         <v>204</v>
       </c>
@@ -8036,7 +8044,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>204</v>
       </c>
@@ -8050,7 +8058,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>204</v>
       </c>
@@ -8064,7 +8072,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>204</v>
       </c>
@@ -8078,7 +8086,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>204</v>
       </c>
@@ -8092,7 +8100,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>204</v>
       </c>
@@ -8106,7 +8114,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>204</v>
       </c>
@@ -8120,7 +8128,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>204</v>
       </c>
@@ -8134,7 +8142,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>204</v>
       </c>
@@ -8148,7 +8156,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>204</v>
       </c>
@@ -8162,7 +8170,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>204</v>
       </c>
@@ -8176,7 +8184,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>204</v>
       </c>
@@ -8190,7 +8198,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>204</v>
       </c>
@@ -8204,7 +8212,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>204</v>
       </c>
@@ -8218,7 +8226,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>204</v>
       </c>
@@ -8232,7 +8240,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
         <v>204</v>
       </c>
@@ -8246,7 +8254,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
         <v>204</v>
       </c>
@@ -8260,7 +8268,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
         <v>204</v>
       </c>
@@ -8274,7 +8282,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
         <v>204</v>
       </c>
@@ -8288,7 +8296,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>204</v>
       </c>
@@ -8302,7 +8310,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
         <v>204</v>
       </c>
@@ -8316,7 +8324,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
         <v>204</v>
       </c>
@@ -8330,7 +8338,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
         <v>204</v>
       </c>
@@ -8344,7 +8352,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
         <v>204</v>
       </c>
@@ -8358,7 +8366,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
         <v>204</v>
       </c>
@@ -8372,7 +8380,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
         <v>204</v>
       </c>
@@ -8386,7 +8394,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
         <v>204</v>
       </c>
@@ -8400,7 +8408,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>204</v>
       </c>
@@ -8414,7 +8422,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>204</v>
       </c>
@@ -8428,7 +8436,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>204</v>
       </c>
@@ -8442,7 +8450,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>204</v>
       </c>
@@ -8456,7 +8464,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>204</v>
       </c>
@@ -8470,7 +8478,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>204</v>
       </c>
@@ -8484,7 +8492,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>204</v>
       </c>
@@ -8498,7 +8506,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
         <v>204</v>
       </c>
@@ -8512,7 +8520,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
         <v>204</v>
       </c>
@@ -8526,7 +8534,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>204</v>
       </c>
@@ -8540,7 +8548,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
         <v>204</v>
       </c>
@@ -8554,7 +8562,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
         <v>204</v>
       </c>
@@ -8568,7 +8576,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
         <v>204</v>
       </c>
@@ -8582,7 +8590,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
         <v>204</v>
       </c>
@@ -8596,7 +8604,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
         <v>204</v>
       </c>
@@ -8610,7 +8618,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
         <v>204</v>
       </c>
@@ -8624,7 +8632,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
         <v>204</v>
       </c>
@@ -8638,7 +8646,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>204</v>
       </c>
@@ -8652,7 +8660,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
         <v>204</v>
       </c>
@@ -8666,7 +8674,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
         <v>204</v>
       </c>
@@ -8680,7 +8688,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>204</v>
       </c>
@@ -8694,7 +8702,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
         <v>204</v>
       </c>
@@ -8708,7 +8716,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
         <v>204</v>
       </c>
@@ -8722,7 +8730,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
         <v>204</v>
       </c>
@@ -8736,7 +8744,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
         <v>204</v>
       </c>
@@ -8750,7 +8758,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
         <v>204</v>
       </c>
@@ -8764,7 +8772,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
         <v>204</v>
       </c>
@@ -8778,7 +8786,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
         <v>204</v>
       </c>
@@ -8792,7 +8800,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
         <v>204</v>
       </c>
@@ -8806,7 +8814,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
         <v>204</v>
       </c>
@@ -8820,7 +8828,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
         <v>204</v>
       </c>
@@ -8834,7 +8842,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
         <v>204</v>
       </c>
@@ -8848,7 +8856,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
         <v>204</v>
       </c>
@@ -8862,7 +8870,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
         <v>204</v>
       </c>
@@ -8876,7 +8884,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
         <v>204</v>
       </c>
@@ -8890,7 +8898,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
         <v>204</v>
       </c>
@@ -8904,7 +8912,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
         <v>204</v>
       </c>
@@ -8918,7 +8926,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
         <v>204</v>
       </c>
@@ -8932,7 +8940,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
         <v>204</v>
       </c>
@@ -8946,7 +8954,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
         <v>204</v>
       </c>
@@ -8960,7 +8968,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
         <v>204</v>
       </c>
@@ -8974,7 +8982,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
         <v>204</v>
       </c>
@@ -8988,7 +8996,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
         <v>204</v>
       </c>
@@ -9002,7 +9010,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
         <v>204</v>
       </c>
@@ -9016,7 +9024,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
         <v>204</v>
       </c>
@@ -9030,7 +9038,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
         <v>204</v>
       </c>
@@ -9044,7 +9052,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
         <v>204</v>
       </c>
@@ -9058,7 +9066,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>204</v>
       </c>
@@ -9072,7 +9080,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
         <v>204</v>
       </c>
@@ -9086,7 +9094,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
         <v>204</v>
       </c>
@@ -9100,7 +9108,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
         <v>204</v>
       </c>
@@ -9114,7 +9122,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
         <v>204</v>
       </c>
@@ -9128,7 +9136,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
         <v>204</v>
       </c>
@@ -9142,7 +9150,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
         <v>204</v>
       </c>
@@ -9156,7 +9164,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
         <v>204</v>
       </c>
@@ -9170,7 +9178,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
         <v>204</v>
       </c>
@@ -9184,7 +9192,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
         <v>204</v>
       </c>
@@ -9198,7 +9206,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
         <v>204</v>
       </c>
@@ -9212,7 +9220,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
         <v>204</v>
       </c>
@@ -9226,7 +9234,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
         <v>216</v>
       </c>
@@ -9240,7 +9248,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
         <v>216</v>
       </c>
@@ -9254,7 +9262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
         <v>216</v>
       </c>
@@ -9268,7 +9276,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
         <v>216</v>
       </c>
@@ -9282,7 +9290,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
         <v>216</v>
       </c>
@@ -9296,7 +9304,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
         <v>216</v>
       </c>
@@ -9310,7 +9318,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
         <v>216</v>
       </c>
@@ -9324,7 +9332,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
         <v>216</v>
       </c>
@@ -9338,7 +9346,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
         <v>216</v>
       </c>
@@ -9352,7 +9360,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
         <v>216</v>
       </c>
@@ -9366,7 +9374,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
         <v>216</v>
       </c>
@@ -9380,7 +9388,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
         <v>216</v>
       </c>
@@ -9394,7 +9402,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
         <v>216</v>
       </c>
@@ -9408,7 +9416,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
         <v>216</v>
       </c>
@@ -9422,7 +9430,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
         <v>216</v>
       </c>
@@ -9436,7 +9444,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
         <v>216</v>
       </c>
@@ -9450,7 +9458,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
         <v>216</v>
       </c>
@@ -9464,7 +9472,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
         <v>216</v>
       </c>
@@ -9478,7 +9486,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
         <v>216</v>
       </c>
@@ -9492,7 +9500,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
         <v>216</v>
       </c>
@@ -9506,7 +9514,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
         <v>216</v>
       </c>
@@ -9520,7 +9528,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
         <v>216</v>
       </c>
@@ -9534,7 +9542,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
         <v>216</v>
       </c>
@@ -9548,7 +9556,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
         <v>216</v>
       </c>
@@ -9562,7 +9570,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
         <v>216</v>
       </c>
@@ -9576,7 +9584,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
         <v>216</v>
       </c>
@@ -9590,7 +9598,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
         <v>216</v>
       </c>
@@ -9604,7 +9612,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
         <v>216</v>
       </c>
@@ -9618,7 +9626,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
         <v>216</v>
       </c>
@@ -9632,7 +9640,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
         <v>216</v>
       </c>
@@ -9646,7 +9654,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
         <v>216</v>
       </c>
@@ -9660,7 +9668,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
         <v>216</v>
       </c>
@@ -9674,7 +9682,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
         <v>216</v>
       </c>
@@ -9688,7 +9696,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
         <v>216</v>
       </c>
@@ -9702,7 +9710,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
         <v>216</v>
       </c>
@@ -9716,7 +9724,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
         <v>216</v>
       </c>
@@ -9730,7 +9738,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
         <v>216</v>
       </c>
@@ -9744,7 +9752,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
         <v>216</v>
       </c>
@@ -9758,7 +9766,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
         <v>216</v>
       </c>
@@ -9772,7 +9780,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
         <v>216</v>
       </c>
@@ -9786,7 +9794,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
         <v>216</v>
       </c>
@@ -9800,7 +9808,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
         <v>216</v>
       </c>
@@ -9814,7 +9822,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
         <v>216</v>
       </c>
@@ -9828,7 +9836,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
         <v>216</v>
       </c>
@@ -9842,7 +9850,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
         <v>216</v>
       </c>
@@ -9856,7 +9864,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
         <v>216</v>
       </c>
@@ -9870,7 +9878,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
         <v>216</v>
       </c>
@@ -9884,7 +9892,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
         <v>216</v>
       </c>
@@ -9898,7 +9906,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
         <v>216</v>
       </c>
@@ -9912,7 +9920,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
         <v>216</v>
       </c>
@@ -9926,7 +9934,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
         <v>216</v>
       </c>
@@ -9940,7 +9948,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
         <v>216</v>
       </c>
@@ -9954,7 +9962,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
         <v>216</v>
       </c>
@@ -9968,7 +9976,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
         <v>216</v>
       </c>
@@ -9982,7 +9990,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
         <v>216</v>
       </c>
@@ -9996,7 +10004,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
         <v>216</v>
       </c>
@@ -10010,7 +10018,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
         <v>216</v>
       </c>
@@ -10024,7 +10032,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
         <v>216</v>
       </c>
@@ -10038,7 +10046,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
         <v>216</v>
       </c>
@@ -10052,7 +10060,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
         <v>216</v>
       </c>
@@ -10066,7 +10074,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
         <v>216</v>
       </c>
@@ -10080,7 +10088,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
         <v>216</v>
       </c>
@@ -10094,7 +10102,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
         <v>216</v>
       </c>
@@ -10108,7 +10116,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
         <v>216</v>
       </c>
@@ -10122,7 +10130,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
         <v>216</v>
       </c>
@@ -10136,7 +10144,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
         <v>216</v>
       </c>
@@ -10150,7 +10158,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
         <v>216</v>
       </c>
@@ -10164,7 +10172,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
         <v>216</v>
       </c>
@@ -10178,7 +10186,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
         <v>216</v>
       </c>
@@ -10192,7 +10200,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
         <v>216</v>
       </c>
@@ -10206,7 +10214,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
         <v>216</v>
       </c>
@@ -10220,7 +10228,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
         <v>216</v>
       </c>
@@ -10234,7 +10242,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
         <v>216</v>
       </c>
@@ -10248,7 +10256,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
         <v>216</v>
       </c>
@@ -10262,7 +10270,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
         <v>216</v>
       </c>
@@ -10276,7 +10284,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
         <v>216</v>
       </c>
@@ -10290,7 +10298,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
         <v>216</v>
       </c>
@@ -10304,7 +10312,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
         <v>216</v>
       </c>
@@ -10318,7 +10326,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
         <v>216</v>
       </c>
@@ -10332,7 +10340,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
         <v>216</v>
       </c>
@@ -10346,7 +10354,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
         <v>216</v>
       </c>
@@ -10360,7 +10368,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
         <v>216</v>
       </c>
@@ -10374,7 +10382,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
         <v>216</v>
       </c>
@@ -10388,7 +10396,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
         <v>216</v>
       </c>
@@ -10402,7 +10410,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
         <v>216</v>
       </c>
@@ -10416,7 +10424,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
         <v>216</v>
       </c>
@@ -10430,7 +10438,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
         <v>216</v>
       </c>
@@ -10444,7 +10452,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
         <v>216</v>
       </c>
@@ -10458,7 +10466,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
         <v>216</v>
       </c>
@@ -10472,7 +10480,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="699" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
         <v>216</v>
       </c>
@@ -10486,7 +10494,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="700" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
         <v>216</v>
       </c>
@@ -10500,7 +10508,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="701" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
         <v>216</v>
       </c>
@@ -10514,7 +10522,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="702" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
         <v>216</v>
       </c>
@@ -10528,7 +10536,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="703" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
         <v>216</v>
       </c>
@@ -10542,7 +10550,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="704" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
         <v>216</v>
       </c>
@@ -10556,7 +10564,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="705" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
         <v>216</v>
       </c>
@@ -10570,7 +10578,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="706" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
         <v>216</v>
       </c>
@@ -10584,7 +10592,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="707" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
         <v>216</v>
       </c>
@@ -10598,7 +10606,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="708" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
         <v>216</v>
       </c>
@@ -10612,7 +10620,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="709" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
         <v>216</v>
       </c>
@@ -10626,7 +10634,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="710" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
         <v>216</v>
       </c>
@@ -10640,7 +10648,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="711" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
         <v>216</v>
       </c>
@@ -10654,7 +10662,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="712" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
         <v>216</v>
       </c>
@@ -10668,7 +10676,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="713" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
         <v>216</v>
       </c>
@@ -10682,7 +10690,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="714" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
         <v>216</v>
       </c>
@@ -10696,7 +10704,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="715" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
         <v>216</v>
       </c>
@@ -10710,7 +10718,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="716" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
         <v>216</v>
       </c>
@@ -10724,7 +10732,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="717" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
         <v>216</v>
       </c>
@@ -10738,7 +10746,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="718" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
         <v>216</v>
       </c>
@@ -10752,7 +10760,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="719" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
         <v>216</v>
       </c>
@@ -10766,7 +10774,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="720" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
         <v>216</v>
       </c>
@@ -10780,7 +10788,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="721" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
         <v>216</v>
       </c>
@@ -10794,7 +10802,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="722" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
         <v>216</v>
       </c>
@@ -10808,7 +10816,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="723" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
         <v>216</v>
       </c>
@@ -10822,7 +10830,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="725" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
         <v>216</v>
       </c>
@@ -10836,7 +10844,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="726" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
         <v>216</v>
       </c>
@@ -10850,7 +10858,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="727" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
         <v>216</v>
       </c>
@@ -10864,7 +10872,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="728" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
         <v>216</v>
       </c>
@@ -10878,7 +10886,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="729" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
         <v>216</v>
       </c>
@@ -10892,7 +10900,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="730" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
         <v>216</v>
       </c>
@@ -10906,7 +10914,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="731" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
         <v>216</v>
       </c>
@@ -10920,7 +10928,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="732" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
         <v>216</v>
       </c>
@@ -10934,7 +10942,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="733" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
         <v>216</v>
       </c>
@@ -10948,7 +10956,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="734" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
         <v>216</v>
       </c>
@@ -10962,7 +10970,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="735" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
         <v>216</v>
       </c>
@@ -10976,7 +10984,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="736" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
         <v>216</v>
       </c>
@@ -10990,7 +10998,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="737" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
         <v>216</v>
       </c>
@@ -11004,7 +11012,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="738" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
         <v>216</v>
       </c>
@@ -11018,7 +11026,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="739" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
         <v>216</v>
       </c>
@@ -11032,7 +11040,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="740" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
         <v>216</v>
       </c>
@@ -11046,7 +11054,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="741" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
         <v>216</v>
       </c>
@@ -11060,7 +11068,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="742" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
         <v>216</v>
       </c>
@@ -11074,7 +11082,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="743" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
         <v>216</v>
       </c>
@@ -11088,7 +11096,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="744" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
         <v>216</v>
       </c>
@@ -11102,7 +11110,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="745" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
         <v>216</v>
       </c>
@@ -11116,7 +11124,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="746" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
         <v>216</v>
       </c>
@@ -11130,7 +11138,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="747" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
         <v>216</v>
       </c>
@@ -11144,7 +11152,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="748" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
         <v>216</v>
       </c>
@@ -11158,7 +11166,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="749" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
         <v>216</v>
       </c>
@@ -11174,20 +11182,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B113"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -11195,7 +11203,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -11203,7 +11211,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -11211,7 +11219,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>61</v>
       </c>
@@ -11219,7 +11227,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -11227,7 +11235,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>135</v>
       </c>
@@ -11235,7 +11243,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>134</v>
       </c>
@@ -11243,7 +11251,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>133</v>
       </c>
@@ -11251,7 +11259,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>163</v>
       </c>
@@ -11259,7 +11267,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>164</v>
       </c>
@@ -11267,7 +11275,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>132</v>
       </c>
@@ -11275,15 +11283,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>232</v>
       </c>
       <c r="B12">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -11291,7 +11299,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -11299,7 +11307,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -11307,7 +11315,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -11315,7 +11323,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -11323,7 +11331,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -11331,7 +11339,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -11339,7 +11347,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -11347,7 +11355,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -11355,7 +11363,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -11363,7 +11371,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -11371,7 +11379,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -11379,7 +11387,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -11387,7 +11395,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>43</v>
       </c>
@@ -11395,7 +11403,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -11403,7 +11411,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>165</v>
       </c>
@@ -11411,7 +11419,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>188</v>
       </c>
@@ -11419,7 +11427,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -11427,7 +11435,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>23</v>
       </c>
@@ -11435,7 +11443,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>62</v>
       </c>
@@ -11443,7 +11451,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -11451,7 +11459,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>64</v>
       </c>
@@ -11459,7 +11467,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>66</v>
       </c>
@@ -11467,7 +11475,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>68</v>
       </c>
@@ -11475,7 +11483,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>71</v>
       </c>
@@ -11483,7 +11491,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>57</v>
       </c>
@@ -11491,7 +11499,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>144</v>
       </c>
@@ -11499,7 +11507,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>141</v>
       </c>
@@ -11507,7 +11515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>142</v>
       </c>
@@ -11515,7 +11523,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>143</v>
       </c>
@@ -11523,7 +11531,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>73</v>
       </c>
@@ -11531,7 +11539,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -11539,7 +11547,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>67</v>
       </c>
@@ -11547,7 +11555,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>65</v>
       </c>
@@ -11555,7 +11563,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>69</v>
       </c>
@@ -11563,7 +11571,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>70</v>
       </c>
@@ -11571,7 +11579,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>76</v>
       </c>
@@ -11579,7 +11587,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>145</v>
       </c>
@@ -11587,7 +11595,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>169</v>
       </c>
@@ -11595,7 +11603,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>193</v>
       </c>
@@ -11603,7 +11611,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>139</v>
       </c>
@@ -11611,7 +11619,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>74</v>
       </c>
@@ -11619,7 +11627,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>77</v>
       </c>
@@ -11627,7 +11635,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -11635,7 +11643,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>59</v>
       </c>
@@ -11643,7 +11651,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>85</v>
       </c>
@@ -11651,7 +11659,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>86</v>
       </c>
@@ -11659,7 +11667,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>87</v>
       </c>
@@ -11667,7 +11675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>152</v>
       </c>
@@ -11675,7 +11683,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>174</v>
       </c>
@@ -11683,7 +11691,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>81</v>
       </c>
@@ -11691,7 +11699,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>172</v>
       </c>
@@ -11699,7 +11707,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>196</v>
       </c>
@@ -11707,7 +11715,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>99</v>
       </c>
@@ -11715,7 +11723,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>98</v>
       </c>
@@ -11723,7 +11731,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>90</v>
       </c>
@@ -11731,7 +11739,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>92</v>
       </c>
@@ -11739,7 +11747,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>93</v>
       </c>
@@ -11747,7 +11755,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>94</v>
       </c>
@@ -11755,7 +11763,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>96</v>
       </c>
@@ -11763,7 +11771,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>91</v>
       </c>
@@ -11771,7 +11779,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>95</v>
       </c>
@@ -11779,7 +11787,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>97</v>
       </c>
@@ -11787,7 +11795,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>101</v>
       </c>
@@ -11795,7 +11803,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>102</v>
       </c>
@@ -11803,7 +11811,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>88</v>
       </c>
@@ -11811,7 +11819,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -11819,7 +11827,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>89</v>
       </c>
@@ -11827,7 +11835,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>82</v>
       </c>
@@ -11835,7 +11843,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>154</v>
       </c>
@@ -11843,7 +11851,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>176</v>
       </c>
@@ -11851,7 +11859,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>175</v>
       </c>
@@ -11859,7 +11867,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>150</v>
       </c>
@@ -11867,7 +11875,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>110</v>
       </c>
@@ -11875,7 +11883,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>111</v>
       </c>
@@ -11883,7 +11891,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>112</v>
       </c>
@@ -11891,7 +11899,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>113</v>
       </c>
@@ -11899,7 +11907,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>114</v>
       </c>
@@ -11907,7 +11915,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>181</v>
       </c>
@@ -11915,7 +11923,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>183</v>
       </c>
@@ -11923,7 +11931,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>184</v>
       </c>
@@ -11931,7 +11939,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>180</v>
       </c>
@@ -11939,7 +11947,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>127</v>
       </c>
@@ -11947,7 +11955,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>126</v>
       </c>
@@ -11955,7 +11963,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>119</v>
       </c>
@@ -11963,7 +11971,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>121</v>
       </c>
@@ -11971,7 +11979,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>116</v>
       </c>
@@ -11979,7 +11987,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>120</v>
       </c>
@@ -11987,7 +11995,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>124</v>
       </c>
@@ -11995,7 +12003,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>123</v>
       </c>
@@ -12003,7 +12011,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>122</v>
       </c>
@@ -12011,7 +12019,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>157</v>
       </c>
@@ -12019,7 +12027,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>158</v>
       </c>
@@ -12027,7 +12035,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>159</v>
       </c>
@@ -12035,7 +12043,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>160</v>
       </c>
@@ -12043,7 +12051,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>106</v>
       </c>
@@ -12051,7 +12059,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>107</v>
       </c>
@@ -12059,7 +12067,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>108</v>
       </c>
@@ -12067,7 +12075,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>115</v>
       </c>
@@ -12075,7 +12083,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>117</v>
       </c>
@@ -12083,7 +12091,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>118</v>
       </c>
@@ -12093,6 +12101,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>